--- a/funding_verification/pools/pools.xlsx
+++ b/funding_verification/pools/pools.xlsx
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Overview'!$A$1:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'P2 Physical AI'!$A$1:$P$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'P2+P3 Robot data &amp; evals'!$A$1:$P$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'P3 Agent quality'!$A$1:$P$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'P3 Agent quality'!$A$1:$P$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'P3 Coding agents'!$A$1:$P$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'P4 Retrieval'!$A$1:$P$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'P4+P5 Legal AI'!$A$1:$P$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'P4+P5 Legal AI'!$A$1:$P$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'P6 Search &amp; optimization'!$A$1:$P$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'P7 Industrial diagrams'!$A$1:$P$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Generic'!$A$1:$P$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Generic'!$A$1:$P$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0</v>
@@ -603,13 +603,13 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>7</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -767,13 +767,13 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>8</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -915,13 +915,13 @@
       <c r="D11" s="3" t="inlineStr"/>
       <c r="E11" s="3" t="inlineStr"/>
       <c r="F11" s="3" t="n">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>40</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
     </row>
@@ -963,7 +963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P105"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2113,27 +2113,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>pocket</t>
+          <t>dedalus-labs</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Pocket</t>
+          <t>Dedalus Labs</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Winter 2026</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Voice AI</t>
+          <t>Agent Infra &amp; Dev Tools</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>AI voice recorder device</t>
+          <t>Compute for agents</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2155,18 +2155,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>AI voice recorder that takes notes in the real world</t>
+          <t>Persistent compute for AI agents</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>consumer hardware and audio product; no remaining proof point applies</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>infrastructure, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>AGENT_EVAL</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Processing hours of in-person audio on a small device forces hard latency and battery tradeoffs.</t>
+          <t>Persistent agent machines need fast snapshot and restore so long tasks survive crashes.</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2181,27 +2185,27 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>dedalus-labs</t>
+          <t>beyond-reach-labs</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Dedalus Labs</t>
+          <t>Beyond Reach Labs</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Winter 2026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Agent Infra &amp; Dev Tools</t>
+          <t>Defense &amp; Space</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Compute for agents</t>
+          <t>Space solar arrays</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2223,22 +2227,18 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Persistent compute for AI agents</t>
+          <t>Space solar arrays that grow in orbit</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>infrastructure, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
+          <t>space hardware, no ML proof point</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Persistent agent machines need fast snapshot and restore so long tasks survive crashes.</t>
+          <t>Arrays at football-field scale make in-orbit structural dynamics the central engineering problem.</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2247,33 +2247,33 @@
         </is>
       </c>
       <c r="P18" s="5" t="n">
-        <v>11000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>beyond-reach-labs</t>
+          <t>qfex</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Beyond Reach Labs</t>
+          <t>QFEX</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Winter 2026</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Defense &amp; Space</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Space solar arrays</t>
+          <t>24/7 exchange</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2295,18 +2295,18 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Space solar arrays that grow in orbit</t>
+          <t>24/7 global stock exchange</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>space hardware, no ML proof point</t>
+          <t>exchange infrastructure, no ML proof point</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Arrays at football-field scale make in-orbit structural dynamics the central engineering problem.</t>
+          <t>Running markets 24/7 on traditional assets makes pricing outside underlying hours the core problem.</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2315,33 +2315,33 @@
         </is>
       </c>
       <c r="P19" s="5" t="n">
-        <v>10000000</v>
+        <v>9500000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>qfex</t>
+          <t>orbital-operations</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>QFEX</t>
+          <t>Orbital Operations</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Defense &amp; Space</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24/7 exchange</t>
+          <t>Satellite defense vehicles</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2363,18 +2363,18 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>24/7 global stock exchange</t>
+          <t>High-thrust reusable vehicles for satellite defense</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>exchange infrastructure, no ML proof point</t>
+          <t>space hardware, no ML proof point</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Running markets 24/7 on traditional assets makes pricing outside underlying hours the core problem.</t>
+          <t>High-thrust maneuvering in orbit makes propulsion reuse and rapid retasking the central problems.</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2383,33 +2383,33 @@
         </is>
       </c>
       <c r="P20" s="5" t="n">
-        <v>9500000</v>
+        <v>8800000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>orbital-operations</t>
+          <t>river-markets</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Orbital Operations</t>
+          <t>River Markets</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Winter 2025</t>
+          <t>Spring 2026</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Defense &amp; Space</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Satellite defense vehicles</t>
+          <t>Prediction markets</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2431,18 +2431,18 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>High-thrust reusable vehicles for satellite defense</t>
+          <t>Prime brokerage across prediction market venues</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>space hardware, no ML proof point</t>
+          <t>trading infrastructure, no ML proof point</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>High-thrust maneuvering in orbit makes propulsion reuse and rapid retasking the central problems.</t>
+          <t>Cross-margining positions across event venues with different settlement rules is the core risk engine problem.</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2451,18 +2451,18 @@
         </is>
       </c>
       <c r="P21" s="5" t="n">
-        <v>8800000</v>
+        <v>8500000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>river-markets</t>
+          <t>insforge-instacloud</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>River Markets</t>
+          <t>InsForge (InstaCloud)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Agent Infra &amp; Dev Tools</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Prediction markets</t>
+          <t>Agent-native cloud</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2499,18 +2499,22 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Prime brokerage across prediction market venues</t>
+          <t>Serverless cloud that coding agents deploy to directly</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>trading infrastructure, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>cloud infrastructure; coding-agent overlap is indirect</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Cross-margining positions across event venues with different settlement rules is the core risk engine problem.</t>
+          <t>Coding agents ship broken backends when the platform gives them no structured runtime feedback on what failed.</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2519,33 +2523,33 @@
         </is>
       </c>
       <c r="P22" s="5" t="n">
-        <v>8500000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>insforge-instacloud</t>
+          <t>catchback-cards</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>InsForge (InstaCloud)</t>
+          <t>CatchBack Cards</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Spring 2026</t>
+          <t>Winter 2026</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Agent Infra &amp; Dev Tools</t>
+          <t>Consumer &amp; Creative AI</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Agent-native cloud</t>
+          <t>Digital collectibles</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2567,22 +2571,18 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Serverless cloud that coding agents deploy to directly</t>
+          <t>Digital collectible pack openings</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>cloud infrastructure; coding-agent overlap is indirect</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
+          <t>consumer product, no ML proof point</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Coding agents ship broken backends when the platform gives them no structured runtime feedback on what failed.</t>
+          <t>Provably fair pack odds backed by real card inventory is the core system design problem.</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2591,18 +2591,18 @@
         </is>
       </c>
       <c r="P23" s="5" t="n">
-        <v>8000000</v>
+        <v>7800000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>catchback-cards</t>
+          <t>didit</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CatchBack Cards</t>
+          <t>Didit</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Consumer &amp; Creative AI</t>
+          <t>Security &amp; Compliance</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Digital collectibles</t>
+          <t>Identity / KYC / fraud</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2639,18 +2639,22 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Digital collectible pack openings</t>
+          <t>Identity verification and fraud APIs</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>consumer product, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>identity infrastructure, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>PHYS</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Provably fair pack odds backed by real card inventory is the core system design problem.</t>
+          <t>Deepfake and document-tampering detection now decides identity verification accuracy.</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2659,33 +2663,33 @@
         </is>
       </c>
       <c r="P24" s="5" t="n">
-        <v>7800000</v>
+        <v>7500000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>didit</t>
+          <t>blaxel</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Didit</t>
+          <t>Blaxel</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Winter 2026</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Security &amp; Compliance</t>
+          <t>Agent Infra &amp; Dev Tools</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Identity / KYC / fraud</t>
+          <t>Agent infrastructure</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2707,22 +2711,22 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Identity verification and fraud APIs</t>
+          <t>Infrastructure for autonomous agents</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>identity infrastructure, no direct proof point</t>
+          <t>infrastructure, no direct proof point</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>PHYS</t>
+          <t>AGENT_EVAL</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Deepfake and document-tampering detection now decides identity verification accuracy.</t>
+          <t>Agent sandboxes need millisecond resume times so tools feel instant inside long tasks.</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2731,33 +2735,33 @@
         </is>
       </c>
       <c r="P25" s="5" t="n">
-        <v>7500000</v>
+        <v>7300000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>blaxel</t>
+          <t>blank-bio</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Blaxel</t>
+          <t>Blank Bio</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Agent Infra &amp; Dev Tools</t>
+          <t>Healthcare &amp; Bio</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Agent infrastructure</t>
+          <t>RNA / clinical trials</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2779,22 +2783,18 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure for autonomous agents</t>
+          <t>RNA models to improve clinical trial success</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>infrastructure, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
+          <t>biology models, no proof point</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Agent sandboxes need millisecond resume times so tools feel instant inside long tasks.</t>
+          <t>RNA models for trial selection must generalize across patient cohorts with very few labeled outcomes.</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2803,33 +2803,33 @@
         </is>
       </c>
       <c r="P26" s="5" t="n">
-        <v>7300000</v>
+        <v>7200000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>blank-bio</t>
+          <t>reditus-space</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Blank Bio</t>
+          <t>Reditus Space</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Bio</t>
+          <t>Defense &amp; Space</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>RNA / clinical trials</t>
+          <t>Reusable satellites</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2851,18 +2851,18 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>RNA models to improve clinical trial success</t>
+          <t>Reusable satellites for zero-g manufacturing</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>biology models, no proof point</t>
+          <t>space hardware, no ML proof point</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>RNA models for trial selection must generalize across patient cohorts with very few labeled outcomes.</t>
+          <t>Reusable reentry vehicles make thermal protection and recovery the core engineering problems.</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2871,33 +2871,33 @@
         </is>
       </c>
       <c r="P27" s="5" t="n">
-        <v>7200000</v>
+        <v>7100000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>reditus-space</t>
+          <t>the-prompting-company</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Reditus Space</t>
+          <t>The Prompting Company</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Winter 2025</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Defense &amp; Space</t>
+          <t>Sales &amp; Marketing AI</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Reusable satellites</t>
+          <t>AI search / agent discovery</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2919,18 +2919,22 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Reusable satellites for zero-g manufacturing</t>
+          <t>Helping products get discovered and used by AI agents</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>space hardware, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>marketing to AI systems, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Reusable reentry vehicles make thermal protection and recovery the core engineering problems.</t>
+          <t>Measuring how often models recommend a product requires sampling answers across prompts and model versions.</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2939,18 +2943,18 @@
         </is>
       </c>
       <c r="P28" s="5" t="n">
-        <v>7100000</v>
+        <v>6500000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>the-prompting-company</t>
+          <t>manufact</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>The Prompting Company</t>
+          <t>Manufact</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2960,12 +2964,12 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Agent Infra &amp; Dev Tools</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>AI search / agent discovery</t>
+          <t>MCP cloud</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2987,22 +2991,22 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Helping products get discovered and used by AI agents</t>
+          <t>Cloud platform for MCP servers and chat plugins</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>marketing to AI systems, no direct proof point</t>
+          <t>infrastructure, no direct proof point</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>AGENT_EVAL</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Measuring how often models recommend a product requires sampling answers across prompts and model versions.</t>
+          <t>MCP servers break silently when tool schemas drift between the model client and the backend.</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3011,33 +3015,33 @@
         </is>
       </c>
       <c r="P29" s="5" t="n">
-        <v>6500000</v>
+        <v>6300000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>manufact</t>
+          <t>corvera</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Manufact</t>
+          <t>Corvera</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Winter 2026</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Agent Infra &amp; Dev Tools</t>
+          <t>Sales &amp; Marketing AI</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>MCP cloud</t>
+          <t>CPG sales</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3059,22 +3063,18 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Cloud platform for MCP servers and chat plugins</t>
+          <t>AI sales engine for CPG brands</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>infrastructure, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
+          <t>sales analytics, no ML proof point</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>MCP servers break silently when tool schemas drift between the model client and the backend.</t>
+          <t>Turning sell-through data into rep actions needs clean store-level joins across messy distributor feeds.</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3083,33 +3083,33 @@
         </is>
       </c>
       <c r="P30" s="5" t="n">
-        <v>6300000</v>
+        <v>6200000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>corvera</t>
+          <t>crunched</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Corvera</t>
+          <t>Crunched</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Winter 2026</t>
+          <t>Fall 2025</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>CPG sales</t>
+          <t>Excel analyst</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -3131,18 +3131,22 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>AI sales engine for CPG brands</t>
+          <t>Excel AI analyst for finance power users</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>sales analytics, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>spreadsheet agent, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>AGENT_EVAL</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Turning sell-through data into rep actions needs clean store-level joins across messy distributor feeds.</t>
+          <t>Excel agents fail on edits that silently break references across sheets and linked models.</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3151,18 +3155,18 @@
         </is>
       </c>
       <c r="P31" s="5" t="n">
-        <v>6200000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>crunched</t>
+          <t>flick</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Crunched</t>
+          <t>Flick</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3172,12 +3176,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Consumer &amp; Creative AI</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Excel analyst</t>
+          <t>AI filmmaking</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3199,22 +3203,18 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Excel AI analyst for finance power users</t>
+          <t>AI filmmaking software</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>spreadsheet agent, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
+          <t>generative video, no perception proof point</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Excel agents fail on edits that silently break references across sheets and linked models.</t>
+          <t>Keeping characters and scenes consistent across shots is the hard part of AI filmmaking.</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3229,27 +3229,27 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>flick</t>
+          <t>agentmail</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Flick</t>
+          <t>AgentMail</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Fall 2025</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Consumer &amp; Creative AI</t>
+          <t>Agent Infra &amp; Dev Tools</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>AI filmmaking</t>
+          <t>Email for agents</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -3271,18 +3271,22 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>AI filmmaking software</t>
+          <t>Email inbox API for AI agents</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>generative video, no perception proof point</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>infrastructure, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>AGENT_EVAL</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Keeping characters and scenes consistent across shots is the hard part of AI filmmaking.</t>
+          <t>Agent inboxes need deliverability and thread parsing that survive real-world email chaos.</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -3297,27 +3301,27 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>agentmail</t>
+          <t>irbc</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>AgentMail</t>
+          <t>IRBC</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Agent Infra &amp; Dev Tools</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Email for agents</t>
+          <t>AI-native bank</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -3339,22 +3343,18 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Email inbox API for AI agents</t>
+          <t>AI-native financial institution</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>infrastructure, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
+          <t>banking, no ML proof point</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Agent inboxes need deliverability and thread parsing that survive real-world email chaos.</t>
+          <t>An AI-native bank needs compliance controls that keep pace with automated account activity.</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -3369,27 +3369,27 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>irbc</t>
+          <t>bindwell</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>IRBC</t>
+          <t>Bindwell</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Healthcare &amp; Bio</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>AI-native bank</t>
+          <t>AI pesticide discovery</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -3411,18 +3411,22 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>AI-native financial institution</t>
+          <t>AI models that discover new pesticides</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>banking, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>molecule discovery; P6 overlap is indirect</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>SEARCH</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>An AI-native bank needs compliance controls that keep pace with automated account activity.</t>
+          <t>Pesticide discovery models must predict field efficacy and safety from few wet-lab results.</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -3437,27 +3441,27 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>bindwell</t>
+          <t>crustdata</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Bindwell</t>
+          <t>Crustdata</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Winter 2025</t>
+          <t>Fall 2024</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Bio</t>
+          <t>Sales &amp; Marketing AI</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>AI pesticide discovery</t>
+          <t>B2B data API</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3479,22 +3483,22 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>AI models that discover new pesticides</t>
+          <t>Real-time B2B company and people data APIs</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>molecule discovery; P6 overlap is indirect</t>
+          <t>data infrastructure, no ML proof point</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SEARCH</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Pesticide discovery models must predict field efficacy and safety from few wet-lab results.</t>
+          <t>Real-time people data depends on resolving the same person across many sources.</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3509,27 +3513,27 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>crustdata</t>
+          <t>cascade-space</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Crustdata</t>
+          <t>Cascade Space</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Fall 2024</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Defense &amp; Space</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>B2B data API</t>
+          <t>Deep space ground stations</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -3551,22 +3555,18 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Real-time B2B company and people data APIs</t>
+          <t>Commercial deep-space ground station network</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>data infrastructure, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
+          <t>space hardware, no ML proof point</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Real-time people data depends on resolving the same person across many sources.</t>
+          <t>Deep-space links make antenna scheduling and weak-signal decoding the core engineering problems.</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -3575,33 +3575,33 @@
         </is>
       </c>
       <c r="P37" s="5" t="n">
-        <v>6000000</v>
+        <v>5900000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>cascade-space</t>
+          <t>laurence</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Cascade Space</t>
+          <t>Laurence</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Winter 2026</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Defense &amp; Space</t>
+          <t>Sales &amp; Marketing AI</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Deep space ground stations</t>
+          <t>Performance marketing</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3623,18 +3623,18 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Commercial deep-space ground station network</t>
+          <t>Autonomous optimization of e-commerce advertising</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>space hardware, no ML proof point</t>
+          <t>ad optimization, no direct proof point</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Deep-space links make antenna scheduling and weak-signal decoding the core engineering problems.</t>
+          <t>Ad optimization agents need attribution that holds up with delayed and noisy conversion data.</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -3643,33 +3643,33 @@
         </is>
       </c>
       <c r="P38" s="5" t="n">
-        <v>5900000</v>
+        <v>5800000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>laurence</t>
+          <t>s2-dev</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Laurence</t>
+          <t>s2.dev</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Winter 2026</t>
+          <t>Fall 2025</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Agent Infra &amp; Dev Tools</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Performance marketing</t>
+          <t>Streaming data API</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3691,18 +3691,18 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Autonomous optimization of e-commerce advertising</t>
+          <t>API for durable real-time streams</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>ad optimization, no direct proof point</t>
+          <t>data infrastructure, no ML proof point</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Ad optimization agents need attribution that holds up with delayed and noisy conversion data.</t>
+          <t>Durable streams at high fan-out make storage tiering and tail latency the core design problem.</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
@@ -3711,23 +3711,23 @@
         </is>
       </c>
       <c r="P39" s="5" t="n">
-        <v>5800000</v>
+        <v>5500000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>s2-dev</t>
+          <t>pgdog</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>s2.dev</t>
+          <t>PgDog</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Fall 2025</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Streaming data API</t>
+          <t>Postgres scaling</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3759,18 +3759,18 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>API for durable real-time streams</t>
+          <t>Sharding engine for PostgreSQL</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>data infrastructure, no ML proof point</t>
+          <t>database infrastructure, no ML proof point</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Durable streams at high fan-out make storage tiering and tail latency the core design problem.</t>
+          <t>Automatic query routing gets hard on cross-shard joins and transactions.</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -3785,27 +3785,27 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>pgdog</t>
+          <t>expanse</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>PgDog</t>
+          <t>Expanse</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Spring 2026</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Agent Infra &amp; Dev Tools</t>
+          <t>AI Compute &amp; Model Infra</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Postgres scaling</t>
+          <t>GPU utilization</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3827,18 +3827,22 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Sharding engine for PostgreSQL</t>
+          <t>Predicting and reclaiming idle GPU capacity</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>database infrastructure, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>GPU scheduling; only indirect overlap with latency work</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>SEARCH</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Automatic query routing gets hard on cross-shard joins and transactions.</t>
+          <t>Predicting job runtimes well enough to backfill idle GPUs without hurting priority workloads is the core scheduling problem.</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -3847,33 +3851,33 @@
         </is>
       </c>
       <c r="P41" s="5" t="n">
-        <v>5500000</v>
+        <v>5300000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>expanse</t>
+          <t>orange-slice</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Expanse</t>
+          <t>Orange Slice</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Spring 2026</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>AI Compute &amp; Model Infra</t>
+          <t>Sales &amp; Marketing AI</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>GPU utilization</t>
+          <t>Sales enrichment</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3895,22 +3899,22 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Predicting and reclaiming idle GPU capacity</t>
+          <t>Agentic sales enrichment spreadsheet</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>GPU scheduling; only indirect overlap with latency work</t>
+          <t>sales data tool, no direct proof point</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>SEARCH</t>
+          <t>AGENT_EVAL</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Predicting job runtimes well enough to backfill idle GPUs without hurting priority workloads is the core scheduling problem.</t>
+          <t>Enrichment columns written by AI need validation, since one wrong join poisons a whole list.</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
@@ -3925,27 +3929,27 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>orange-slice</t>
+          <t>artificial-societies</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Orange Slice</t>
+          <t>Artificial Societies</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Enterprise Agents &amp; Workflow</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Sales enrichment</t>
+          <t>Society simulation</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3967,22 +3971,18 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Agentic sales enrichment spreadsheet</t>
+          <t>Foundation model of human societies for decisions</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>sales data tool, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
+          <t>simulation model, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Enrichment columns written by AI need validation, since one wrong join poisons a whole list.</t>
+          <t>Simulated populations are only useful when their responses are validated against real survey outcomes.</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3997,27 +3997,27 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>artificial-societies</t>
+          <t>panta</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Artificial Societies</t>
+          <t>Panta</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Winter 2025</t>
+          <t>Winter 2026</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Agents &amp; Workflow</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Society simulation</t>
+          <t>Commercial insurance brokerage</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -4039,18 +4039,22 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Foundation model of human societies for decisions</t>
+          <t>AI-native commercial insurance brokerage</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>simulation model, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>brokerage operations, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Simulated populations are only useful when their responses are validated against real survey outcomes.</t>
+          <t>Commercial submissions require pulling exposure data from loss runs and applications in dozens of formats.</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -4059,23 +4063,23 @@
         </is>
       </c>
       <c r="P44" s="5" t="n">
-        <v>5300000</v>
+        <v>5200000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>panta</t>
+          <t>astor</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Panta</t>
+          <t>Astor</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Winter 2026</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -4085,7 +4089,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Commercial insurance brokerage</t>
+          <t>Retail investing advisor</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -4107,22 +4111,18 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>AI-native commercial insurance brokerage</t>
+          <t>AI investment advisor for retail investors</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>brokerage operations, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
+          <t>consumer finance, no proof point</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Commercial submissions require pulling exposure data from loss runs and applications in dozens of formats.</t>
+          <t>Retail advice agents must keep suitability rules intact while answering open-ended portfolio questions.</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -4131,33 +4131,33 @@
         </is>
       </c>
       <c r="P45" s="5" t="n">
-        <v>5200000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>astor</t>
+          <t>better-auth</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Astor</t>
+          <t>Better Auth</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Agent Infra &amp; Dev Tools</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Retail investing advisor</t>
+          <t>Auth framework</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -4179,18 +4179,18 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>AI investment advisor for retail investors</t>
+          <t>Authentication framework for TypeScript</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>consumer finance, no proof point</t>
+          <t>developer infrastructure, no ML proof point</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr"/>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Retail advice agents must keep suitability rules intact while answering open-ended portfolio questions.</t>
+          <t>Auth frameworks win on edge cases in session handling across frameworks and runtimes.</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>better-auth</t>
+          <t>synthio-labs</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Better Auth</t>
+          <t>Synthio Labs</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Agent Infra &amp; Dev Tools</t>
+          <t>Healthcare &amp; Bio</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Auth framework</t>
+          <t>Pharma GTM</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -4247,18 +4247,22 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Authentication framework for TypeScript</t>
+          <t>Agentic AI for pharma go-to-market teams</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>developer infrastructure, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>pharma GTM, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Auth frameworks win on edge cases in session handling across frameworks and runtimes.</t>
+          <t>Pharma conversations must stay inside approved claims, so every response needs grounding in cleared content.</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -4273,27 +4277,27 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>synthio-labs</t>
+          <t>salespatriot</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Synthio Labs</t>
+          <t>SalesPatriot</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Bio</t>
+          <t>Supply Chain &amp; Industrial Ops AI</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Pharma GTM</t>
+          <t>Distributor back office</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -4315,12 +4319,12 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Agentic AI for pharma go-to-market teams</t>
+          <t>AI back-office system for distributors and OEMs</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>pharma GTM, no direct proof point</t>
+          <t>distribution operations, no direct proof point</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -4330,7 +4334,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Pharma conversations must stay inside approved claims, so every response needs grounding in cleared content.</t>
+          <t>Distributor quoting depends on parsing government RFQs and part specs accurately.</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
@@ -4345,27 +4349,27 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>salespatriot</t>
+          <t>kelai</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>SalesPatriot</t>
+          <t>KelAI</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Winter 2025</t>
+          <t>Spring 2026</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain &amp; Industrial Ops AI</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Distributor back office</t>
+          <t>AI quant</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -4387,22 +4391,22 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>AI back-office system for distributors and OEMs</t>
+          <t>Autonomous quant research engine</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>distribution operations, no direct proof point</t>
+          <t>alpha research, no direct proof point</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>SEARCH</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Distributor quoting depends on parsing government RFQs and part specs accurately.</t>
+          <t>Separating real alpha from overfit signals is the hardest problem in autonomous strategy search.</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -4411,33 +4415,33 @@
         </is>
       </c>
       <c r="P49" s="5" t="n">
-        <v>5000000</v>
+        <v>4975000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>kelai</t>
+          <t>mantis</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>KelAI</t>
+          <t>Mantis</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Spring 2026</t>
+          <t>Winter 2026</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Healthcare &amp; Bio</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>AI quant</t>
+          <t>Human digital twins</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -4459,12 +4463,12 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Autonomous quant research engine</t>
+          <t>Digital twins of humans combining LLMs with physics simulation</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>alpha research, no direct proof point</t>
+          <t>simulation modeling; P6 overlap is indirect</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -4474,7 +4478,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Separating real alpha from overfit signals is the hardest problem in autonomous strategy search.</t>
+          <t>LLM-driven physiology simulation needs calibration against sparse data from each individual.</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -4483,18 +4487,18 @@
         </is>
       </c>
       <c r="P50" s="5" t="n">
-        <v>4975000</v>
+        <v>4824999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>mantis</t>
+          <t>10x-science</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Mantis</t>
+          <t>10x Science</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4509,7 +4513,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Human digital twins</t>
+          <t>Protein characterization</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -4531,22 +4535,18 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Digital twins of humans combining LLMs with physics simulation</t>
+          <t>AI models for protein characterization</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>simulation modeling; P6 overlap is indirect</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>SEARCH</t>
-        </is>
-      </c>
+          <t>biology models, no proof point</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>LLM-driven physiology simulation needs calibration against sparse data from each individual.</t>
+          <t>Protein characterization models must handle sparse, noisy assay data from very different experimental setups.</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
@@ -4555,33 +4555,33 @@
         </is>
       </c>
       <c r="P51" s="5" t="n">
-        <v>4824999</v>
+        <v>4800000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>10x-science</t>
+          <t>alice-tech</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>10x Science</t>
+          <t>Alice.tech</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Winter 2026</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Bio</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Protein characterization</t>
+          <t>Exam prep</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -4603,18 +4603,18 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>AI models for protein characterization</t>
+          <t>AI-driven exam prep from course materials</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>biology models, no proof point</t>
+          <t>education product, no proof point</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Protein characterization models must handle sparse, noisy assay data from very different experimental setups.</t>
+          <t>Personalized exam prep must map course material to exactly what each exam tests.</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
@@ -4629,27 +4629,27 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>alice-tech</t>
+          <t>getbalance</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Alice.tech</t>
+          <t>Balance</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Winter 2025</t>
+          <t>Winter 2026</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Exam prep</t>
+          <t>AI accounting</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -4671,18 +4671,22 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>AI-driven exam prep from course materials</t>
+          <t>AI accounting firm that closes SMB books</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>education product, no proof point</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>accounting operations, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>AGENT_EVAL</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Personalized exam prep must map course material to exactly what each exam tests.</t>
+          <t>Reconciliation agents fail on the long tail of vendor-specific transaction descriptions.</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
@@ -4691,23 +4695,23 @@
         </is>
       </c>
       <c r="P53" s="5" t="n">
-        <v>4800000</v>
+        <v>4700000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>getbalance</t>
+          <t>ruvo</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Ruvo</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Winter 2026</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -4717,7 +4721,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>AI accounting</t>
+          <t>Cross-border / stablecoin</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -4739,22 +4743,18 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>AI accounting firm that closes SMB books</t>
+          <t>Global dollar account for Brazil</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>accounting operations, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
+          <t>payments, no ML proof point</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Reconciliation agents fail on the long tail of vendor-specific transaction descriptions.</t>
+          <t>Settling between Pix, stablecoins and USD rails in real time makes liquidity management the core problem.</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
@@ -4763,23 +4763,23 @@
         </is>
       </c>
       <c r="P54" s="5" t="n">
-        <v>4700000</v>
+        <v>4600000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ruvo</t>
+          <t>kita</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Ruvo</t>
+          <t>Kita</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Winter 2026</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Cross-border / stablecoin</t>
+          <t>Emerging-market underwriting</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -4811,18 +4811,22 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Global dollar account for Brazil</t>
+          <t>Underwriting emerging-market borrowers from financial documents</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>payments, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>document-based underwriting, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Settling between Pix, stablecoins and USD rails in real time makes liquidity management the core problem.</t>
+          <t>Bank statements in emerging markets vary so much in layout that extraction accuracy sets underwriting quality.</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
@@ -4831,33 +4835,33 @@
         </is>
       </c>
       <c r="P55" s="5" t="n">
-        <v>4600000</v>
+        <v>4500000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>kita</t>
+          <t>uplane</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Kita</t>
+          <t>Uplane</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Winter 2026</t>
+          <t>Fall 2025</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Sales &amp; Marketing AI</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Emerging-market underwriting</t>
+          <t>Ad generation</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -4879,22 +4883,18 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Underwriting emerging-market borrowers from financial documents</t>
+          <t>AI that replaces marketing agencies</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>document-based underwriting, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
+          <t>ad generation, no ML proof point</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Bank statements in emerging markets vary so much in layout that extraction accuracy sets underwriting quality.</t>
+          <t>Steering budget toward the few ad variants that convert is harder than generating hundreds of them.</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
@@ -4909,27 +4909,27 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>uplane</t>
+          <t>munify</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Uplane</t>
+          <t>Munify</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Fall 2025</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Ad generation</t>
+          <t>Neobank</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -4951,18 +4951,18 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>AI that replaces marketing agencies</t>
+          <t>Cross-border neobank for the Middle East</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>ad generation, no ML proof point</t>
+          <t>banking, no ML proof point</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Steering budget toward the few ad variants that convert is harder than generating hundreds of them.</t>
+          <t>Onboarding diaspora customers across jurisdictions makes KYC coverage the main scaling constraint.</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4977,27 +4977,27 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>munify</t>
+          <t>maritime-fusion</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Munify</t>
+          <t>Maritime Fusion</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Energy &amp; Industrial Hard Tech</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Neobank</t>
+          <t>Fusion for ships</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -5019,18 +5019,18 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Cross-border neobank for the Middle East</t>
+          <t>Fusion reactors for ships</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>banking, no ML proof point</t>
+          <t>fusion hardware, no ML proof point</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Onboarding diaspora customers across jurisdictions makes KYC coverage the main scaling constraint.</t>
+          <t>Shipboard fusion makes compact magnet design and shielding mass the central problems.</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
@@ -5045,27 +5045,27 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>maritime-fusion</t>
+          <t>orthogonal</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Maritime Fusion</t>
+          <t>Orthogonal</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Winter 2025</t>
+          <t>Winter 2026</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Energy &amp; Industrial Hard Tech</t>
+          <t>Agent Infra &amp; Dev Tools</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Fusion for ships</t>
+          <t>Agentic payments for APIs</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -5087,18 +5087,22 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Fusion reactors for ships</t>
+          <t>Payments that let agents pay for APIs</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>fusion hardware, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>payments infrastructure, no ML proof point</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>AGENT_EVAL</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Shipboard fusion makes compact magnet design and shielding mass the central problems.</t>
+          <t>Per-call agent payments need spend controls that add no latency to each request.</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -5107,18 +5111,18 @@
         </is>
       </c>
       <c r="P59" s="5" t="n">
-        <v>4500000</v>
+        <v>4300000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>orthogonal</t>
+          <t>haladir</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Orthogonal</t>
+          <t>Haladir</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5128,12 +5132,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Agent Infra &amp; Dev Tools</t>
+          <t>Supply Chain &amp; Industrial Ops AI</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Agentic payments for APIs</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -5155,22 +5159,22 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Payments that let agents pay for APIs</t>
+          <t>AI decisions on top of warehouse and transport systems</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>payments infrastructure, no ML proof point</t>
+          <t>logistics data systems, no direct proof point</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>AGENT_EVAL</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Per-call agent payments need spend controls that add no latency to each request.</t>
+          <t>Logistics decisions depend on joining WMS, TMS and ERP records that disagree about the same shipment.</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
@@ -5185,27 +5189,27 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>haladir</t>
+          <t>leadbay</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Haladir</t>
+          <t>Leadbay</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Winter 2026</t>
+          <t>Fall 2025</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain &amp; Industrial Ops AI</t>
+          <t>Sales &amp; Marketing AI</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Lead qualification</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -5227,22 +5231,18 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>AI decisions on top of warehouse and transport systems</t>
+          <t>Qualifying B2B leads for agentic workflows</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>logistics data systems, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
+          <t>lead scoring, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Logistics decisions depend on joining WMS, TMS and ERP records that disagree about the same shipment.</t>
+          <t>Lead qualification models drift quickly as each customer's ideal profile shifts.</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
@@ -5257,27 +5257,27 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>leadbay</t>
+          <t>apolink</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Leadbay</t>
+          <t>Apolink</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Fall 2025</t>
+          <t>Fall 2024</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Defense &amp; Space</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Lead qualification</t>
+          <t>Satellite data relay</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -5299,18 +5299,18 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Qualifying B2B leads for agentic workflows</t>
+          <t>Real-time satellite data relay in low Earth orbit</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>lead scoring, no direct proof point</t>
+          <t>space hardware, no ML proof point</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Lead qualification models drift quickly as each customer's ideal profile shifts.</t>
+          <t>Continuous relay coverage in LEO makes inter-satellite link handoff the core engineering problem.</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
@@ -5325,27 +5325,27 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>apolink</t>
+          <t>subimage</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Apolink</t>
+          <t>SubImage</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Fall 2024</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Defense &amp; Space</t>
+          <t>Security &amp; Compliance</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Satellite data relay</t>
+          <t>Security graph</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -5367,18 +5367,18 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Real-time satellite data relay in low Earth orbit</t>
+          <t>Open-core security graph of infrastructure</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>space hardware, no ML proof point</t>
+          <t>security infrastructure, no ML proof point</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Continuous relay coverage in LEO makes inter-satellite link handoff the core engineering problem.</t>
+          <t>Infrastructure graphs are only trusted when asset relationships stay current across every cloud account.</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -5387,33 +5387,33 @@
         </is>
       </c>
       <c r="P63" s="5" t="n">
-        <v>4300000</v>
+        <v>4200000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>willow</t>
+          <t>golpo</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Willow</t>
+          <t>Golpo</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Voice AI</t>
+          <t>Consumer &amp; Creative AI</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Voice dictation</t>
+          <t>Explainer video generation</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -5435,18 +5435,18 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Voice dictation that replaces the keyboard</t>
+          <t>AI whiteboard explainer videos from documents</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>dictation product; no remaining proof point applies</t>
+          <t>video generation, no proof point</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Dictation feels instant only when transcription and cleanup land within a few hundred milliseconds.</t>
+          <t>Explainer videos stay coherent only when narration and drawing order follow the source document's logic.</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
@@ -5455,33 +5455,33 @@
         </is>
       </c>
       <c r="P64" s="5" t="n">
-        <v>4200000</v>
+        <v>4100000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>subimage</t>
+          <t>burnt</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SubImage</t>
+          <t>burnt</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Winter 2025</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Security &amp; Compliance</t>
+          <t>Supply Chain &amp; Industrial Ops AI</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Security graph</t>
+          <t>Food supply chain</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -5503,18 +5503,22 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Open-core security graph of infrastructure</t>
+          <t>Agentic operating system for food supply chains</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>security infrastructure, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>supply chain operations, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Infrastructure graphs are only trusted when asset relationships stay current across every cloud account.</t>
+          <t>Order entry agents in food distribution must handle emailed orders full of shorthand and substitutions.</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5523,33 +5527,33 @@
         </is>
       </c>
       <c r="P65" s="5" t="n">
-        <v>4200000</v>
+        <v>3800000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>golpo</t>
+          <t>zalos</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Golpo</t>
+          <t>Zalos</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Fall 2025</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Consumer &amp; Creative AI</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Explainer video generation</t>
+          <t>Finance department agents</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -5571,18 +5575,22 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>AI whiteboard explainer videos from documents</t>
+          <t>AI workers that run enterprise finance tasks</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>video generation, no proof point</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>finance operations, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>AGENT_EVAL</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Explainer videos stay coherent only when narration and drawing order follow the source document's logic.</t>
+          <t>Finance agents must show a clear audit trail for every number they post.</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
@@ -5591,33 +5599,33 @@
         </is>
       </c>
       <c r="P66" s="5" t="n">
-        <v>4100000</v>
+        <v>3600000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>burnt</t>
+          <t>unusual</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>burnt</t>
+          <t>Unusual</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Fall 2024</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain &amp; Industrial Ops AI</t>
+          <t>Sales &amp; Marketing AI</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Food supply chain</t>
+          <t>Marketing to AI agents</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -5639,22 +5647,18 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Agentic operating system for food supply chains</t>
+          <t>Marketing to AI agents</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>supply chain operations, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
+          <t>marketing analytics, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Order entry agents in food distribution must handle emailed orders full of shorthand and substitutions.</t>
+          <t>Brands need to know how models describe them, which requires systematic sampling across models and prompts.</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -5663,18 +5667,18 @@
         </is>
       </c>
       <c r="P67" s="5" t="n">
-        <v>3800000</v>
+        <v>3600000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>zalos</t>
+          <t>miniswap</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Zalos</t>
+          <t>Miniswap</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5684,12 +5688,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Consumer &amp; Creative AI</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Finance department agents</t>
+          <t>Hobby marketplace</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -5711,22 +5715,18 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>AI workers that run enterprise finance tasks</t>
+          <t>Marketplace for complex hobby items</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>finance operations, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
+          <t>marketplace, no ML proof point</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Finance agents must show a clear audit trail for every number they post.</t>
+          <t>Identifying exact miniatures and paint states from listing photos is the hard catalog problem in hobby marketplaces.</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -5735,33 +5735,33 @@
         </is>
       </c>
       <c r="P68" s="5" t="n">
-        <v>3600000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>unusual</t>
+          <t>sira</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Unusual</t>
+          <t>Sira</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Fall 2024</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Enterprise Agents &amp; Workflow</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Marketing to AI agents</t>
+          <t>HR / payroll for deskless</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -5783,18 +5783,18 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Marketing to AI agents</t>
+          <t>HR, scheduling and payroll for hourly teams</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>marketing analytics, no direct proof point</t>
+          <t>HR software, no ML proof point</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr"/>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Brands need to know how models describe them, which requires systematic sampling across models and prompts.</t>
+          <t>Scheduling for hourly teams has to respect labor rules that change by city and state.</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
@@ -5803,33 +5803,33 @@
         </is>
       </c>
       <c r="P69" s="5" t="n">
-        <v>3600000</v>
+        <v>3400000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>miniswap</t>
+          <t>finto-de</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Miniswap</t>
+          <t>Finto</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Fall 2025</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Consumer &amp; Creative AI</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Hobby marketplace</t>
+          <t>Enterprise accounting</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -5851,18 +5851,22 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Marketplace for complex hobby items</t>
+          <t>AI accounting for enterprise finance teams</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>marketplace, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>accounting automation, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>AGENT_EVAL</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Identifying exact miniatures and paint states from listing photos is the hard catalog problem in hobby marketplaces.</t>
+          <t>Invoice-to-pay automation fails on matching invoices to POs when line items do not align.</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -5871,33 +5875,33 @@
         </is>
       </c>
       <c r="P70" s="5" t="n">
-        <v>3500000</v>
+        <v>3400000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>uplift-ai</t>
+          <t>general-learning</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Uplift AI</t>
+          <t>General Learning</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Fall 2024</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Voice AI</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Regional-language voice models</t>
+          <t>AI tutors</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -5919,18 +5923,18 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Voice models for regional languages</t>
+          <t>AI tutors for major school curricula</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>speech model training; no remaining proof point applies</t>
+          <t>education product, no proof point</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Low-resource languages make natural prosody and code-switching the hardest parts of regional voice models.</t>
+          <t>AI tutors must align explanations to each curriculum's mark schemes, which generic models ignore.</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5939,33 +5943,33 @@
         </is>
       </c>
       <c r="P71" s="5" t="n">
-        <v>3500000</v>
+        <v>3400000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>sira</t>
+          <t>blindpay</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Sira</t>
+          <t>BlindPay</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Agents &amp; Workflow</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>HR / payroll for deskless</t>
+          <t>Stablecoin payments API</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -5987,18 +5991,18 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>HR, scheduling and payroll for hourly teams</t>
+          <t>Stablecoin API for global payments</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>HR software, no ML proof point</t>
+          <t>payments, no ML proof point</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Scheduling for hourly teams has to respect labor rules that change by city and state.</t>
+          <t>Stablecoin payouts need local off-ramps with reliable settlement times in every corridor.</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -6007,23 +6011,23 @@
         </is>
       </c>
       <c r="P72" s="5" t="n">
-        <v>3400000</v>
+        <v>3300000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>finto-de</t>
+          <t>oddpool</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Finto</t>
+          <t>Oddpool</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Spring 2026</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -6033,7 +6037,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Enterprise accounting</t>
+          <t>Prediction markets</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -6055,22 +6059,18 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>AI accounting for enterprise finance teams</t>
+          <t>Institutional infrastructure for prediction markets</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>accounting automation, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
+          <t>trading data infrastructure, no ML proof point</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Invoice-to-pay automation fails on matching invoices to POs when line items do not align.</t>
+          <t>Matching equivalent contracts across prediction venues with different wording is the core data problem.</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -6079,33 +6079,33 @@
         </is>
       </c>
       <c r="P73" s="5" t="n">
-        <v>3400000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>general-learning</t>
+          <t>cedar</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>General Learning</t>
+          <t>Cedar</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Fall 2024</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Sales &amp; Marketing AI</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>AI tutors</t>
+          <t>Sales playbooks</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -6127,18 +6127,18 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>AI tutors for major school curricula</t>
+          <t>Sales playbook execution for GTM teams</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>education product, no proof point</t>
+          <t>sales enablement, no proof point</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>AI tutors must align explanations to each curriculum's mark schemes, which generic models ignore.</t>
+          <t>Spreading a top rep's playbook needs call analysis that finds what actually moved deals.</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
@@ -6147,18 +6147,18 @@
         </is>
       </c>
       <c r="P74" s="5" t="n">
-        <v>3400000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>blindpay</t>
+          <t>bluebook</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>BlindPay</t>
+          <t>Bluebook</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Stablecoin payments API</t>
+          <t>Accounting firms</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -6195,18 +6195,22 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Stablecoin API for global payments</t>
+          <t>AI agents for accounting firms</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>payments, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>accounting operations, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Stablecoin payouts need local off-ramps with reliable settlement times in every corridor.</t>
+          <t>Accounting agents must reconcile against client ledgers that each follow different conventions.</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
@@ -6215,23 +6219,23 @@
         </is>
       </c>
       <c r="P75" s="5" t="n">
-        <v>3300000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>oddpool</t>
+          <t>ralo</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Oddpool</t>
+          <t>Ralo</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Spring 2026</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -6241,7 +6245,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Prediction markets</t>
+          <t>Mortgage broker</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -6263,18 +6267,18 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Institutional infrastructure for prediction markets</t>
+          <t>AI-native mortgage broker</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>trading data infrastructure, no ML proof point</t>
+          <t>brokerage, no direct proof point</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Matching equivalent contracts across prediction venues with different wording is the core data problem.</t>
+          <t>An AI mortgage broker must collect and verify borrower documents faster than a human processor.</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -6283,33 +6287,33 @@
         </is>
       </c>
       <c r="P76" s="5" t="n">
-        <v>3000000</v>
+        <v>2900000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>cedar</t>
+          <t>metreecs</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Cedar</t>
+          <t>Metreecs</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Winter 2025</t>
+          <t>Fall 2024</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Supply Chain &amp; Industrial Ops AI</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Sales playbooks</t>
+          <t>Retail demand forecasting</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -6331,18 +6335,18 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Sales playbook execution for GTM teams</t>
+          <t>AI demand forecasting for retail</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>sales enablement, no proof point</t>
+          <t>forecasting, no proof point</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Spreading a top rep's playbook needs call analysis that finds what actually moved deals.</t>
+          <t>Retail forecasting fails on new products and promotions that have no sales history.</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -6351,18 +6355,18 @@
         </is>
       </c>
       <c r="P77" s="5" t="n">
-        <v>3000000</v>
+        <v>2700000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>bluebook</t>
+          <t>contrario</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Bluebook</t>
+          <t>Contrario</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6372,12 +6376,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Enterprise Agents &amp; Workflow</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Accounting firms</t>
+          <t>Recruiting</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -6399,22 +6403,18 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>AI agents for accounting firms</t>
+          <t>AI hiring platform with expert recruiters</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>accounting operations, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
+          <t>recruiting, no proof point</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Accounting agents must reconcile against client ledgers that each follow different conventions.</t>
+          <t>AI candidate matching must beat keyword filters on signal that resumes do not state directly.</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -6423,33 +6423,33 @@
         </is>
       </c>
       <c r="P78" s="5" t="n">
-        <v>3000000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>ralo</t>
+          <t>avora</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Ralo</t>
+          <t>Avora</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Fall 2024</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Healthcare &amp; Bio</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Mortgage broker</t>
+          <t>Dental operations</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -6471,18 +6471,22 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>AI-native mortgage broker</t>
+          <t>Agents that improve case acceptance for dental groups</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>brokerage, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>dental operations, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>RAG</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>An AI mortgage broker must collect and verify borrower documents faster than a human processor.</t>
+          <t>Case acceptance agents need treatment plans and patient history joined correctly across practice systems.</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6491,33 +6495,33 @@
         </is>
       </c>
       <c r="P79" s="5" t="n">
-        <v>2900000</v>
+        <v>2300000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>metreecs</t>
+          <t>athenahq</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Metreecs</t>
+          <t>AthenaHQ</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Fall 2024</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain &amp; Industrial Ops AI</t>
+          <t>Sales &amp; Marketing AI</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Retail demand forecasting</t>
+          <t>AI search SEO</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -6539,18 +6543,18 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>AI demand forecasting for retail</t>
+          <t>Brand visibility in AI search answers</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>forecasting, no proof point</t>
+          <t>marketing analytics, no direct proof point</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Retail forecasting fails on new products and promotions that have no sales history.</t>
+          <t>Tracking AI search visibility requires sampling model answers at scale as models change weekly.</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
@@ -6559,18 +6563,18 @@
         </is>
       </c>
       <c r="P80" s="5" t="n">
-        <v>2700000</v>
+        <v>2200000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>contrario</t>
+          <t>exin-therapeutics</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Contrario</t>
+          <t>Exin Therapeutics</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6580,12 +6584,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Agents &amp; Workflow</t>
+          <t>Healthcare &amp; Bio</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Recruiting</t>
+          <t>Neuro drug discovery</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -6607,18 +6611,18 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>AI hiring platform with expert recruiters</t>
+          <t>AI drug discovery for neurotherapeutics</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>recruiting, no proof point</t>
+          <t>drug discovery, no proof point</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>AI candidate matching must beat keyword filters on signal that resumes do not state directly.</t>
+          <t>Linking neural activity readouts in mice to human therapeutic effect is the core translation problem.</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
@@ -6627,33 +6631,33 @@
         </is>
       </c>
       <c r="P81" s="5" t="n">
-        <v>2300000</v>
+        <v>2162300</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>avora</t>
+          <t>mercura</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Avora</t>
+          <t>Mercura</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Fall 2024</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Bio</t>
+          <t>Supply Chain &amp; Industrial Ops AI</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Dental operations</t>
+          <t>Distributor quoting</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -6675,12 +6679,12 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Agents that improve case acceptance for dental groups</t>
+          <t>Quote and order automation for construction distributors</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>dental operations, no direct proof point</t>
+          <t>order automation, no direct proof point</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -6690,7 +6694,7 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Case acceptance agents need treatment plans and patient history joined correctly across practice systems.</t>
+          <t>Construction quotes arrive as specs and drawings, so matching them to SKUs is the core problem.</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
@@ -6699,33 +6703,33 @@
         </is>
       </c>
       <c r="P82" s="5" t="n">
-        <v>2300000</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>athenahq</t>
+          <t>groundcontrol</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>AthenaHQ</t>
+          <t>GroundControl</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Winter 2025</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Supply Chain &amp; Industrial Ops AI</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>AI search SEO</t>
+          <t>Regulated manufacturing</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -6747,18 +6751,22 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Brand visibility in AI search answers</t>
+          <t>Software for highly regulated manufacturing</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>marketing analytics, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>manufacturing software, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>DIAGRAM</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Tracking AI search visibility requires sampling model answers at scale as models change weekly.</t>
+          <t>Regulated manufacturing records must tie each step to its spec revision, which breaks with paper travelers.</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -6767,33 +6775,33 @@
         </is>
       </c>
       <c r="P83" s="5" t="n">
-        <v>2200000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>exin-therapeutics</t>
+          <t>freestyle-ai</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Exin Therapeutics</t>
+          <t>Freestyle</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Winter 2025</t>
+          <t>Fall 2024</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Bio</t>
+          <t>Consumer &amp; Creative AI</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Neuro drug discovery</t>
+          <t>Email assistant</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -6815,18 +6823,22 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>AI drug discovery for neurotherapeutics</t>
+          <t>AI assistant for Gmail</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>drug discovery, no proof point</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>consumer productivity, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>AGENT_EVAL</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Linking neural activity readouts in mice to human therapeutic effect is the core translation problem.</t>
+          <t>Email assistants earn trust only when drafts sound like the user and never misstate commitments.</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -6835,33 +6847,33 @@
         </is>
       </c>
       <c r="P84" s="5" t="n">
-        <v>2162300</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>mercura</t>
+          <t>origami-2</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Mercura</t>
+          <t>Origami</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Winter 2025</t>
+          <t>Fall 2024</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain &amp; Industrial Ops AI</t>
+          <t>Sales &amp; Marketing AI</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Distributor quoting</t>
+          <t>Customer acquisition agents</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -6883,22 +6895,18 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Quote and order automation for construction distributors</t>
+          <t>AI that finds customers from a company's domain</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>order automation, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
+          <t>sales prospecting, no proof point</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Construction quotes arrive as specs and drawings, so matching them to SKUs is the core problem.</t>
+          <t>Prospecting agents are useful only when their leads match real buying signals.</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -6907,33 +6915,33 @@
         </is>
       </c>
       <c r="P85" s="5" t="n">
-        <v>2100000</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>groundcontrol</t>
+          <t>afternoon-co</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>GroundControl</t>
+          <t>Afternoon.co</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Fall 2024</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain &amp; Industrial Ops AI</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Regulated manufacturing</t>
+          <t>Founder bookkeeping</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -6955,22 +6963,18 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Software for highly regulated manufacturing</t>
+          <t>Bookkeeping, compliance and tax for founders</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>manufacturing software, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr">
-        <is>
-          <t>DIAGRAM</t>
-        </is>
-      </c>
+          <t>accounting service, no proof point</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Regulated manufacturing records must tie each step to its spec revision, which breaks with paper travelers.</t>
+          <t>Real-time founder metrics depend on categorizing transactions correctly the day they land.</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
@@ -6985,27 +6989,27 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>freestyle-ai</t>
+          <t>chrt</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Freestyle</t>
+          <t>chrt</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Fall 2024</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Consumer &amp; Creative AI</t>
+          <t>Supply Chain &amp; Industrial Ops AI</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Email assistant</t>
+          <t>Time-critical logistics</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -7027,22 +7031,18 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>AI assistant for Gmail</t>
+          <t>Logistics for time-critical shipping</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>consumer productivity, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
+          <t>logistics, no ML proof point</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Email assistants earn trust only when drafts sound like the user and never misstate commitments.</t>
+          <t>Time-critical shipping depends on predicting handoff delays across carriers in real time.</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -7051,33 +7051,33 @@
         </is>
       </c>
       <c r="P87" s="5" t="n">
-        <v>2000000</v>
+        <v>1453000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>origami-2</t>
+          <t>mochatrade</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Origami</t>
+          <t>Mochatrade</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Fall 2024</t>
+          <t>Spring 2026</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Customer acquisition agents</t>
+          <t>Trading / perps</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -7099,18 +7099,18 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>AI that finds customers from a company's domain</t>
+          <t>Global access to US stocks through perpetual futures</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>sales prospecting, no proof point</t>
+          <t>trading infrastructure, no ML proof point</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr"/>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Prospecting agents are useful only when their leads match real buying signals.</t>
+          <t>Pricing equity perpetuals across market closes and overnight gaps is the hardest risk problem in the product.</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
@@ -7119,23 +7119,23 @@
         </is>
       </c>
       <c r="P88" s="5" t="n">
-        <v>2000000</v>
+        <v>1158000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>afternoon-co</t>
+          <t>cifrato</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Afternoon.co</t>
+          <t>Cifrato</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Fall 2024</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Founder bookkeeping</t>
+          <t>Accounting firms</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -7167,18 +7167,22 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Bookkeeping, compliance and tax for founders</t>
+          <t>AI accountant for accounting firms</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>accounting service, no proof point</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>accounting automation, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>AGENT_EVAL</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Real-time founder metrics depend on categorizing transactions correctly the day they land.</t>
+          <t>Invoice capture agents fail on low-quality scans and inconsistent supplier formats.</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
@@ -7187,33 +7191,33 @@
         </is>
       </c>
       <c r="P89" s="5" t="n">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>chrt</t>
+          <t>opennote</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>chrt</t>
+          <t>Opennote</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain &amp; Industrial Ops AI</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Time-critical logistics</t>
+          <t>AI notebook</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -7235,18 +7239,18 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Logistics for time-critical shipping</t>
+          <t>Notebook with a built-in AI thinking partner</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>logistics, no ML proof point</t>
+          <t>consumer education tool, no proof point</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr"/>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Time-critical shipping depends on predicting handoff delays across carriers in real time.</t>
+          <t>An AI thinking partner is useful only when its edits respect the student's own reasoning.</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -7255,33 +7259,33 @@
         </is>
       </c>
       <c r="P90" s="5" t="n">
-        <v>1453000</v>
+        <v>850000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>caretta</t>
+          <t>spaceflow-technologies-inc</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Caretta</t>
+          <t>SpaceFlow Technologies, Inc.</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Winter 2026</t>
+          <t>Summer 2026</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Supply Chain &amp; Industrial Ops AI</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Realtime sales-call copilot</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -7303,57 +7307,55 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Real-time AI assistance during live sales calls</t>
+          <t>Automating procurement for physical-goods businesses</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>real-time call assist; no remaining proof point applies</t>
+          <t>procurement operations, no matching technical proof point</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>AGENT_EVAL</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Live call assist has to surface an answer within a second of the question or the rep has moved on.</t>
+          <t>Supplier quotes arrive in every format, so normalizing line items is the core extraction problem in procurement automation.</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P91" s="5" t="n">
-        <v>1300000</v>
-      </c>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="P91" s="5" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>mochatrade</t>
+          <t>rise-reforming</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Mochatrade</t>
+          <t>Rise Reforming</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Spring 2026</t>
+          <t>Summer 2026</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Energy &amp; Industrial Hard Tech</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Trading / perps</t>
+          <t>Waste gas to chemicals</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -7375,53 +7377,51 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Global access to US stocks through perpetual futures</t>
+          <t>Chemical process that turns waste gases into chemicals</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>trading infrastructure, no ML proof point</t>
+          <t>process chemistry, no ML proof point</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Pricing equity perpetuals across market closes and overnight gaps is the hardest risk problem in the product.</t>
+          <t>Catalyst stability under variable waste-gas composition decides whether a reforming process survives outside the lab.</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P92" s="5" t="n">
-        <v>1158000</v>
-      </c>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="P92" s="5" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>cifrato</t>
+          <t>logical</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Cifrato</t>
+          <t>Logical</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Winter 2025</t>
+          <t>Fall 2025</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Consumer &amp; Creative AI</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Accounting firms</t>
+          <t>Desktop copilot</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>AI accountant for accounting firms</t>
+          <t>Proactive desktop copilot</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>accounting automation, no direct proof point</t>
+          <t>consumer assistant, no direct proof point</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -7458,42 +7458,40 @@
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Invoice capture agents fail on low-quality scans and inconsistent supplier formats.</t>
+          <t>A proactive copilot lives or dies on deciding when to interrupt the user.</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P93" s="5" t="n">
-        <v>1000000</v>
-      </c>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="P93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>opennote</t>
+          <t>dome</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Opennote</t>
+          <t>Dome</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Fall 2025</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>AI notebook</t>
+          <t>Prediction market API</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -7515,53 +7513,51 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Notebook with a built-in AI thinking partner</t>
+          <t>Unified API for prediction markets</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>consumer education tool, no proof point</t>
+          <t>market data infrastructure, no ML proof point</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>An AI thinking partner is useful only when its edits respect the student's own reasoning.</t>
+          <t>Normalizing order books and contract metadata across Kalshi and Polymarket is the core API problem.</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P94" s="5" t="n">
-        <v>850000</v>
-      </c>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="P94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>spaceflow-technologies-inc</t>
+          <t>vibeflow</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>SpaceFlow Technologies, Inc.</t>
+          <t>VibeFlow</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Summer 2026</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain &amp; Industrial Ops AI</t>
+          <t>Sales &amp; Marketing AI</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Procurement</t>
+          <t>Social content</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -7583,22 +7579,18 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Automating procurement for physical-goods businesses</t>
+          <t>AI content manager for social media</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>procurement operations, no matching technical proof point</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
+          <t>content generation, no ML proof point</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Supplier quotes arrive in every format, so normalizing line items is the core extraction problem in procurement automation.</t>
+          <t>Viral social content depends on fast feedback from engagement data, which generation alone cannot provide.</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
@@ -7611,27 +7603,27 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>rise-reforming</t>
+          <t>getasap</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Rise Reforming</t>
+          <t>GETASAP</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Summer 2026</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Energy &amp; Industrial Hard Tech</t>
+          <t>Supply Chain &amp; Industrial Ops AI</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Waste gas to chemicals</t>
+          <t>Fresh produce logistics</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -7653,18 +7645,18 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Chemical process that turns waste gases into chemicals</t>
+          <t>Fresh produce logistics</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>process chemistry, no ML proof point</t>
+          <t>logistics, no ML proof point</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Catalyst stability under variable waste-gas composition decides whether a reforming process survives outside the lab.</t>
+          <t>Fresh produce routing is a race against spoilage, so demand forecasting drives every routing decision.</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -7677,27 +7669,27 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>logical</t>
+          <t>scalar-field</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Logical</t>
+          <t>Scalar Field</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Fall 2025</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Consumer &amp; Creative AI</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Desktop copilot</t>
+          <t>Agentic trading</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -7719,22 +7711,18 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>Proactive desktop copilot</t>
+          <t>Agentic trading desk</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>consumer assistant, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
+          <t>trading, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>A proactive copilot lives or dies on deciding when to interrupt the user.</t>
+          <t>Agentic trading needs guardrails that stop a model from compounding a bad position.</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
@@ -7747,27 +7735,27 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>dome</t>
+          <t>forge-automation</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Dome</t>
+          <t>Forge Automation</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Fall 2025</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Energy &amp; Industrial Hard Tech</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Prediction market API</t>
+          <t>Automated CNC factory</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -7789,18 +7777,22 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Unified API for prediction markets</t>
+          <t>Software-driven CNC parts factories</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>market data infrastructure, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>manufacturing automation, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>PHYS</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Normalizing order books and contract metadata across Kalshi and Polymarket is the core API problem.</t>
+          <t>Four-day custom parts depend on automated CAM programming from each customer's CAD.</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
@@ -7813,27 +7805,27 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>vibeflow</t>
+          <t>nitrode</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>VibeFlow</t>
+          <t>Nitrode</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Consumer &amp; Creative AI</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Social content</t>
+          <t>Game development AI</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -7855,18 +7847,22 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>AI content manager for social media</t>
+          <t>Frontier AI research for game development</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>content generation, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>game AI research, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>AGENT_EVAL</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Viral social content depends on fast feedback from engagement data, which generation alone cannot provide.</t>
+          <t>Game-building models need training data that captures how game logic and assets fit together.</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
@@ -7879,27 +7875,27 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>getasap</t>
+          <t>asteroid</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>GETASAP</t>
+          <t>Asteroid</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain &amp; Industrial Ops AI</t>
+          <t>Healthcare &amp; Bio</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Fresh produce logistics</t>
+          <t>Healthcare integrations</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -7921,18 +7917,22 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>Fresh produce logistics</t>
+          <t>Integration layer for EHRs and payer portals</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>logistics, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>healthcare integration, no direct proof point</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>AGENT_EVAL</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Fresh produce routing is a race against spoilage, so demand forecasting drives every routing decision.</t>
+          <t>Payer portal automation breaks whenever a portal changes its layout or login flow.</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
@@ -7945,27 +7945,27 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>scalar-field</t>
+          <t>inversion-semiconductor</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Scalar Field</t>
+          <t>Inversion Semiconductor</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Winter 2025</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Energy &amp; Industrial Hard Tech</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Agentic trading</t>
+          <t>Chip fabrication</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -7987,18 +7987,18 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>Agentic trading desk</t>
+          <t>Next-generation chip fabrication machines</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>trading, no direct proof point</t>
+          <t>semiconductor hardware, no ML proof point</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Agentic trading needs guardrails that stop a model from compounding a bad position.</t>
+          <t>Faster lithography tools live or die on overlay accuracy at production throughput.</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
@@ -8008,284 +8008,8 @@
       </c>
       <c r="P101" s="5" t="n"/>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>forge-automation</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Forge Automation</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Winter 2025</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Energy &amp; Industrial Hard Tech</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>Automated CNC factory</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>GENERIC</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Generic (no proof point)</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr"/>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>Software-driven CNC parts factories</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>manufacturing automation, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t>PHYS</t>
-        </is>
-      </c>
-      <c r="N102" s="2" t="inlineStr">
-        <is>
-          <t>Four-day custom parts depend on automated CAM programming from each customer's CAD.</t>
-        </is>
-      </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="P102" s="5" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>nitrode</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Nitrode</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Winter 2025</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Consumer &amp; Creative AI</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>Game development AI</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>GENERIC</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>Generic (no proof point)</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr"/>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>Frontier AI research for game development</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>game AI research, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>Game-building models need training data that captures how game logic and assets fit together.</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="P103" s="5" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>asteroid</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Asteroid</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Winter 2025</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Healthcare &amp; Bio</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Healthcare integrations</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>GENERIC</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>Generic (no proof point)</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>Integration layer for EHRs and payer portals</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>healthcare integration, no direct proof point</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
-      <c r="N104" s="2" t="inlineStr">
-        <is>
-          <t>Payer portal automation breaks whenever a portal changes its layout or login flow.</t>
-        </is>
-      </c>
-      <c r="O104" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="P104" s="5" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>inversion-semiconductor</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Inversion Semiconductor</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Winter 2025</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Energy &amp; Industrial Hard Tech</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>Chip fabrication</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>GENERIC</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Generic (no proof point)</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>Next-generation chip fabrication machines</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>semiconductor hardware, no ML proof point</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
-      <c r="N105" s="2" t="inlineStr">
-        <is>
-          <t>Faster lithography tools live or die on overlay accuracy at production throughput.</t>
-        </is>
-      </c>
-      <c r="O105" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="P105" s="5" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P105"/>
+  <autoFilter ref="A1:P101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10256,7 +9980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11170,27 +10894,27 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>telli</t>
+          <t>characterquilt</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>telli</t>
+          <t>CharacterQuilt</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Fall 2024</t>
+          <t>Spring 2026</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Voice AI</t>
+          <t>Sales &amp; Marketing AI</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Customer-facing voice agents</t>
+          <t>Marketing campaign agents</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -11216,22 +10940,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>AI agents that run customer-facing calls and operations</t>
+          <t>Computer-use agents that deploy enterprise marketing campaigns</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>conversational agents need evaluation and quality systems -&gt; P3</t>
+          <t>computer-use agents need eval harnesses -&gt; P3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>GENERIC</t>
+          <t>CODE</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Outbound call agents need evals on real call transcripts, since one bad script path repeats across thousands of calls.</t>
+          <t>Computer-use agents break on UI drift in ad platforms, so replayable evals on real campaign flows matter most.</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -11240,33 +10964,33 @@
         </is>
       </c>
       <c r="P13" s="5" t="n">
-        <v>15000000</v>
+        <v>9795824</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>veritus</t>
+          <t>kaizen</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Veritus</t>
+          <t>Kaizen</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Summer 2025</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Healthcare &amp; Bio</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Loan servicing agents</t>
+          <t>Patient referral processing</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11292,22 +11016,18 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Voice and text agents for loan servicing and collections</t>
+          <t>Digital employee that processes patient referrals</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>regulated collections agents need evaluation and QA -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
+          <t>web automation agents -&gt; P3</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Collections agents must stay inside compliance scripts, so every conversation needs automated policy scoring.</t>
+          <t>Referral agents must read faxes and portals reliably, since one missed field delays care.</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -11316,33 +11036,33 @@
         </is>
       </c>
       <c r="P14" s="5" t="n">
-        <v>10100000</v>
+        <v>8500000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>characterquilt</t>
+          <t>cotool</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CharacterQuilt</t>
+          <t>Cotool</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Spring 2026</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Security &amp; Compliance</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Marketing campaign agents</t>
+          <t>SecOps agents</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -11368,12 +11088,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Computer-use agents that deploy enterprise marketing campaigns</t>
+          <t>AI agents for security operations teams</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>computer-use agents need eval harnesses -&gt; P3</t>
+          <t>security agents need quality systems -&gt; P3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -11383,7 +11103,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Computer-use agents break on UI drift in ad platforms, so replayable evals on real campaign flows matter most.</t>
+          <t>SecOps agents must close alerts correctly at scale, so precision on real alert history is the metric that matters.</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -11392,18 +11112,18 @@
         </is>
       </c>
       <c r="P15" s="5" t="n">
-        <v>9795824</v>
+        <v>7400000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>kaizen</t>
+          <t>eloquent-ai</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Kaizen</t>
+          <t>Eloquent AI</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -11413,12 +11133,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Healthcare &amp; Bio</t>
+          <t>Fintech &amp; Financial Ops</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Patient referral processing</t>
+          <t>Financial services operations</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -11444,18 +11164,18 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Digital employee that processes patient referrals</t>
+          <t>AI operators for regulated financial services operations</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>web automation agents -&gt; P3</t>
+          <t>agent reliability in regulated workflows -&gt; P3</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Referral agents must read faxes and portals reliably, since one missed field delays care.</t>
+          <t>Regulated operations need agents whose every action is auditable and reproducible under review.</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -11464,18 +11184,18 @@
         </is>
       </c>
       <c r="P16" s="5" t="n">
-        <v>8500000</v>
+        <v>7400000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>cotool</t>
+          <t>sim</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Cotool</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -11485,12 +11205,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Security &amp; Compliance</t>
+          <t>Enterprise Agents &amp; Workflow</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>SecOps agents</t>
+          <t>Agent builder</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -11516,22 +11236,18 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>AI agents for security operations teams</t>
+          <t>Platform to build autonomous agents for enterprise systems</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>security agents need quality systems -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>CODE</t>
-        </is>
-      </c>
+          <t>agent quality -&gt; P3</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>SecOps agents must close alerts correctly at scale, so precision on real alert history is the metric that matters.</t>
+          <t>Enterprise agent builders need evals tied to each connected system, or failures surface only in production.</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -11540,33 +11256,33 @@
         </is>
       </c>
       <c r="P17" s="5" t="n">
-        <v>7400000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>eloquent-ai</t>
+          <t>lua-global-inc</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Eloquent AI</t>
+          <t>Lua Global Inc</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Fall 2025</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Enterprise Agents &amp; Workflow</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Financial services operations</t>
+          <t>Mid-market agent platform</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -11592,18 +11308,18 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>AI operators for regulated financial services operations</t>
+          <t>Agent platform for mid-market companies</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>agent reliability in regulated workflows -&gt; P3</t>
+          <t>agent reliability at scale -&gt; P3</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Regulated operations need agents whose every action is auditable and reproducible under review.</t>
+          <t>Enterprise reliability for agents comes from regression evals on real conversations before every model or prompt change.</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -11612,33 +11328,33 @@
         </is>
       </c>
       <c r="P18" s="5" t="n">
-        <v>7400000</v>
+        <v>5800000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>oncactus</t>
+          <t>gpt</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Nexus</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Fall 2025</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Enterprise Agents &amp; Workflow</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Growth for trades</t>
+          <t>No-code agent builder</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -11664,22 +11380,18 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>AI answering service that captures every call for trades businesses</t>
+          <t>No-code builder for production AI agents</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>call-handling agents need evaluation on real calls -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>GENERIC</t>
-        </is>
-      </c>
+          <t>agent quality for non-technical builders -&gt; P3</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Answering agents for trades need QA on real calls, since a misrouted emergency job loses the customer.</t>
+          <t>No-code agent builders need built-in evals, since non-technical owners cannot debug a failing agent themselves.</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -11688,33 +11400,33 @@
         </is>
       </c>
       <c r="P19" s="5" t="n">
-        <v>7000000</v>
+        <v>4300000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>sim</t>
+          <t>lingodotdev</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Lingo.dev</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Fall 2024</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Agents &amp; Workflow</t>
+          <t>Agent Infra &amp; Dev Tools</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Agent builder</t>
+          <t>Localization</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -11740,18 +11452,18 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Platform to build autonomous agents for enterprise systems</t>
+          <t>Localization engineering platform with LLM translation</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>agent quality -&gt; P3</t>
+          <t>measuring LLM translation quality = evals -&gt; P3</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Enterprise agent builders need evals tied to each connected system, or failures surface only in production.</t>
+          <t>LLM localization is reliable only with automated quality scoring that catches terminology drift.</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -11760,18 +11472,18 @@
         </is>
       </c>
       <c r="P20" s="5" t="n">
-        <v>7000000</v>
+        <v>4200000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>flai</t>
+          <t>truthsystems</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Flai</t>
+          <t>truthsystems</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -11781,12 +11493,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Sales &amp; Marketing AI</t>
+          <t>Security &amp; Compliance</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Dealership lead handling</t>
+          <t>AI governance</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -11812,22 +11524,18 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>AI that answers dealership leads after hours</t>
+          <t>Real-time governance agents for generative AI use</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>lead-handling agents need evaluation -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>GENERIC</t>
-        </is>
-      </c>
+          <t>policy enforcement on AI usage = agent quality -&gt; P3</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Dealership lead agents need evals on real conversations, since a wrong price or stock answer loses the sale.</t>
+          <t>Governance agents must block risky prompts in real time without flagging so much that people route around them.</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -11836,23 +11544,23 @@
         </is>
       </c>
       <c r="P21" s="5" t="n">
-        <v>6000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>lua-global-inc</t>
+          <t>flowscope</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Lua Global Inc</t>
+          <t>flowscope</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Fall 2025</t>
+          <t>Spring 2026</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -11862,7 +11570,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Mid-market agent platform</t>
+          <t>AI implementation services</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11888,18 +11596,18 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Agent platform for mid-market companies</t>
+          <t>Deploying agents that automate business processes reliably</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>agent reliability at scale -&gt; P3</t>
+          <t>process automation agents need quality systems -&gt; P3</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Enterprise reliability for agents comes from regression evals on real conversations before every model or prompt change.</t>
+          <t>Process automation agents need regression tests on real process traces before every change ships.</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -11908,23 +11616,23 @@
         </is>
       </c>
       <c r="P22" s="5" t="n">
-        <v>5800000</v>
+        <v>3800000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>lance</t>
+          <t>trace-so</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Lance</t>
+          <t>Trace</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Winter 2026</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -11934,7 +11642,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Hotel operations</t>
+          <t>Human-agent orchestration</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -11960,22 +11668,18 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>AI agents that answer calls and run hotel operations</t>
+          <t>Orchestrating work between humans and AI agents</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>hotel operations agents need quality systems -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>GENERIC</t>
-        </is>
-      </c>
+          <t>agent workflow quality -&gt; P3</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Hotel agents that close bookings need evals on real guest conversations, since errors cost revenue directly.</t>
+          <t>Shared context across systems is what keeps multi-agent workflows from repeating or contradicting work.</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -11984,33 +11688,33 @@
         </is>
       </c>
       <c r="P23" s="5" t="n">
-        <v>5000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>leaping-ai</t>
+          <t>novoflow</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Leaping AI</t>
+          <t>Novoflow</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Winter 2025</t>
+          <t>Spring 2025</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Voice AI</t>
+          <t>Healthcare &amp; Bio</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Voice and text agents</t>
+          <t>Healthcare ops agents</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -12036,22 +11740,18 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Voice and text agents for customer service</t>
+          <t>Computer-using agents on medical practice EHRs</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>customer service agents need evaluation harnesses -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>GENERIC</t>
-        </is>
-      </c>
+          <t>computer-use agent reliability -&gt; P3</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Support agents across voice and text need one eval suite, or quality drifts differently on each channel.</t>
+          <t>Computer-use agents on EHRs break on UI changes, so replayable evals on real workflows are essential.</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -12060,33 +11760,33 @@
         </is>
       </c>
       <c r="P24" s="5" t="n">
-        <v>4700000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>avallon-ai</t>
+          <t>tryjanet</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Avallon AI</t>
+          <t>Janet AI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Spring 2025</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Fintech &amp; Financial Ops</t>
+          <t>Enterprise Agents &amp; Workflow</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Insurance claims</t>
+          <t>Company agents</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -12104,11 +11804,7 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Moderate</t>
@@ -12116,22 +11812,18 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>AI agents for insurance claims calls and documents</t>
+          <t>Agents that learn a company and work around the clock</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>claims agents need evaluation and QA -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
+          <t>agent reliability with custom models -&gt; P3</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Claims agents must capture loss details accurately, so every intake needs automated checks against policy terms.</t>
+          <t>Agents running 24/7 need evals that catch silent quality regressions after each custom model update.</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -12140,33 +11832,33 @@
         </is>
       </c>
       <c r="P25" s="5" t="n">
-        <v>4662000</v>
+        <v>2225000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>gpt</t>
+          <t>notte</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Nexus</t>
+          <t>Notte</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Fall 2025</t>
+          <t>Summer 2025</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Enterprise Agents &amp; Workflow</t>
+          <t>Agent Infra &amp; Dev Tools</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>No-code agent builder</t>
+          <t>Browser infra for agents</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -12192,765 +11884,33 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>No-code builder for production AI agents</t>
+          <t>Cloud browser infrastructure for AI agents</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>agent quality for non-technical builders -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>browser agent reliability -&gt; P3</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>GENERIC</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>No-code agent builders need built-in evals, since non-technical owners cannot debug a failing agent themselves.</t>
+          <t>Browser agents break on authentication flows, so reliable session handling decides task success.</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="n">
-        <v>4300000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>lingodotdev</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Lingo.dev</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Fall 2024</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Agent Infra &amp; Dev Tools</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Localization</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Agent quality and evaluation</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Localization engineering platform with LLM translation</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>measuring LLM translation quality = evals -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>LLM localization is reliable only with automated quality scoring that catches terminology drift.</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="n">
-        <v>4200000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>truthsystems</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>truthsystems</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Summer 2025</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Security &amp; Compliance</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>AI governance</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Agent quality and evaluation</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Real-time governance agents for generative AI use</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>policy enforcement on AI usage = agent quality -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>Governance agents must block risky prompts in real time without flagging so much that people route around them.</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v>4000000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>flowscope</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>flowscope</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Spring 2026</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise Agents &amp; Workflow</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>AI implementation services</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Agent quality and evaluation</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Deploying agents that automate business processes reliably</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>process automation agents need quality systems -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>Process automation agents need regression tests on real process traces before every change ships.</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v>3800000</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>patientdeskai</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Patientdesk.ai</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Winter 2026</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Healthcare &amp; Bio</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Dental front office</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Agent quality and evaluation</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>AI front and back office agent for dental practices</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>booking agents need quality checks on real calls -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>GENERIC</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>Dental booking agents must get insurance and appointment details right, so every call needs automated QA.</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>3800000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>freya</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Freya</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Summer 2025</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Voice AI</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise voice agents</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Agent quality and evaluation</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Voice AI agents for enterprises</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>enterprise conversational agents need quality systems -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>GENERIC</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise call agents need regression evals on real conversations before every prompt or model change ships.</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P31" s="5" t="n">
-        <v>3500000</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>trace-so</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Trace</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Summer 2025</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise Agents &amp; Workflow</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Human-agent orchestration</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Agent quality and evaluation</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Orchestrating work between humans and AI agents</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>agent workflow quality -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>Shared context across systems is what keeps multi-agent workflows from repeating or contradicting work.</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>novoflow</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Novoflow</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Spring 2025</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Healthcare &amp; Bio</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Healthcare ops agents</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Agent quality and evaluation</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Computer-using agents on medical practice EHRs</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>computer-use agent reliability -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>Computer-use agents on EHRs break on UI changes, so replayable evals on real workflows are essential.</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>tryjanet</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Janet AI</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Summer 2025</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise Agents &amp; Workflow</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Company agents</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Agent quality and evaluation</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Agents that learn a company and work around the clock</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>agent reliability with custom models -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>Agents running 24/7 need evals that catch silent quality regressions after each custom model update.</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v>2225000</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>stormy</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Stormy</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Summer 2025</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise Agents &amp; Workflow</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Office ops for trades</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Agent quality and evaluation</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Answering every call and running the office for trades businesses</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>office agents need quality checks on real jobs -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>GENERIC</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>Trades office agents must capture job details correctly, so quoting errors need to be caught before follow-up.</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v>1700000</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>notte</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Notte</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Summer 2025</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Agent Infra &amp; Dev Tools</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Browser infra for agents</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>AGENT_EVAL</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Agent quality and evaluation</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Cloud browser infrastructure for AI agents</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>browser agent reliability -&gt; P3</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>GENERIC</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>Browser agents break on authentication flows, so reliable session handling decides task success.</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
           <t>Unclear</t>
         </is>
       </c>
-      <c r="P36" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P36"/>
+  <autoFilter ref="A1:P26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16295,7 +15255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16981,12 +15941,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>caseflood-ai</t>
+          <t>gale</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Caseflood.ai</t>
+          <t>Gale</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -17001,7 +15961,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Law firm intake</t>
+          <t>Immigration</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -17027,22 +15987,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Intake for elite law firms</t>
+          <t>Data-driven immigration platform for US companies</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>law firm intake AI = legal AI work -&gt; P4+P5</t>
+          <t>immigration filings built from legal documents -&gt; P4+P5</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>AGENT_EVAL</t>
+          <t>GENERIC</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Law firm intake has to qualify cases in real time and capture facts that hold up at case review.</t>
+          <t>Visa petitions succeed on evidence assembly, so retrieving the right supporting documents drives approval rates.</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -17051,18 +16011,18 @@
         </is>
       </c>
       <c r="P10" s="5" t="n">
-        <v>3200000</v>
+        <v>2700000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>gale</t>
+          <t>overstand-labs</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Gale</t>
+          <t>Overstand Labs</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -17072,12 +16032,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Legal AI</t>
+          <t>Enterprise Agents &amp; Workflow</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Immigration</t>
+          <t>Large-data navigation</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -17103,109 +16063,33 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Data-driven immigration platform for US companies</t>
+          <t>Navigating very large datasets quickly for legal work</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>immigration filings built from legal documents -&gt; P4+P5</t>
+          <t>large legal data review -&gt; P4+P5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>GENERIC</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Visa petitions succeed on evidence assembly, so retrieving the right supporting documents drives approval rates.</t>
+          <t>Navigating discovery-scale datasets fast depends on retrieval that surfaces relevant documents without full review.</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v>2700000</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>overstand-labs</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Overstand Labs</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Winter 2025</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise Agents &amp; Workflow</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Large-data navigation</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Legal AI over legal documents</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>P4 + P5</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Navigating very large datasets quickly for legal work</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>large legal data review -&gt; P4+P5</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>RAG</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>Navigating discovery-scale datasets fast depends on retrieval that surfaces relevant documents without full review.</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
           <t>Unclear</t>
         </is>
       </c>
-      <c r="P12" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P12"/>
+  <autoFilter ref="A1:P11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
